--- a/originales/respuestas/2025/01. Calificadas/root/Empresa Metro De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Empresa Metro De Bogotá.xlsx
@@ -424,7 +424,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -433,7 +433,7 @@
     <t>Espacios de ideación y cocreación con los equipos internos., Procesos de formación o capacitaciones en metodologías de innovación., Creación de equipos o laboratorios de innovación internos.</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -562,7 +562,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -579,6 +579,15 @@
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
@@ -673,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -731,16 +740,29 @@
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2211,11 +2233,17 @@
         <v>6.6383492617E10</v>
       </c>
       <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="K4" s="8">
+        <v>5.0</v>
+      </c>
       <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
+      <c r="M4" s="8">
+        <v>5.0</v>
+      </c>
       <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
+      <c r="O4" s="8">
+        <v>5.0</v>
+      </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
@@ -2262,11 +2290,17 @@
         <v>8.9402289654E10</v>
       </c>
       <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="K5" s="8">
+        <v>5.0</v>
+      </c>
       <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
+      <c r="M5" s="8">
+        <v>5.0</v>
+      </c>
       <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="O5" s="8">
+        <v>5.0</v>
+      </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
@@ -2360,11 +2394,17 @@
         <v>2.055679855E9</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="K7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="M7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
+      <c r="O7" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P7" s="10"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
@@ -2462,11 +2502,17 @@
         <v>2.15414516E9</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
+      <c r="M9" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="O9" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
@@ -2609,11 +2655,17 @@
         <v>1.80459E17</v>
       </c>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="8">
+        <v>2.0</v>
+      </c>
       <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="M12" s="8">
+        <v>2.0</v>
+      </c>
       <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="O12" s="8">
+        <v>2.0</v>
+      </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2660,11 +2712,17 @@
         <v>8.07038E16</v>
       </c>
       <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
+      <c r="K13" s="12">
+        <v>2.0</v>
+      </c>
       <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
+      <c r="M13" s="12">
+        <v>2.0</v>
+      </c>
       <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
+      <c r="O13" s="12">
+        <v>2.0</v>
+      </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2756,11 +2814,17 @@
         <v>2.055679855E9</v>
       </c>
       <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="K15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
+      <c r="M15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
+      <c r="O15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
@@ -2858,11 +2922,11 @@
         <v>55</v>
       </c>
       <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="K17" s="8"/>
       <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="M17" s="8"/>
       <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="O17" s="8"/>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
@@ -2909,11 +2973,17 @@
         <v>2.15414516E9</v>
       </c>
       <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+      <c r="K18" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
+      <c r="M18" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
+      <c r="O18" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
@@ -3005,11 +3075,17 @@
         <v>216.0</v>
       </c>
       <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
+      <c r="K20" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="M20" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+      <c r="O20" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
@@ -3056,11 +3132,17 @@
         <v>226.0</v>
       </c>
       <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
+      <c r="K21" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
+      <c r="M21" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
+      <c r="O21" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
@@ -3107,11 +3189,17 @@
         <v>8.0</v>
       </c>
       <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
+      <c r="K22" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
+      <c r="M22" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
+      <c r="O22" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -3158,11 +3246,17 @@
         <v>8.0</v>
       </c>
       <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
+      <c r="K23" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
+      <c r="M23" s="8">
+        <v>3.0</v>
+      </c>
       <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
+      <c r="O23" s="8">
+        <v>3.0</v>
+      </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
@@ -3260,11 +3354,17 @@
         <v>180.0</v>
       </c>
       <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
+      <c r="K25" s="12">
+        <v>2.0</v>
+      </c>
       <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
+      <c r="M25" s="12">
+        <v>2.0</v>
+      </c>
       <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
+      <c r="O25" s="12">
+        <v>2.0</v>
+      </c>
       <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3311,11 +3411,17 @@
         <v>151.0</v>
       </c>
       <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="K26" s="8">
+        <v>2.0</v>
+      </c>
       <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
+      <c r="M26" s="8">
+        <v>2.0</v>
+      </c>
       <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
+      <c r="O26" s="8">
+        <v>2.0</v>
+      </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3362,11 +3468,17 @@
         <v>5.0</v>
       </c>
       <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
+      <c r="K27" s="12">
+        <v>4.0</v>
+      </c>
       <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
+      <c r="M27" s="12">
+        <v>4.0</v>
+      </c>
       <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
+      <c r="O27" s="12">
+        <v>4.0</v>
+      </c>
       <c r="P27" s="10"/>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3413,11 +3525,17 @@
         <v>7.0</v>
       </c>
       <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
+      <c r="K28" s="8">
+        <v>4.0</v>
+      </c>
       <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
+      <c r="M28" s="8">
+        <v>4.0</v>
+      </c>
       <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
+      <c r="O28" s="8">
+        <v>4.0</v>
+      </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -4644,7 +4762,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="31" width="10.71"/>
+    <col customWidth="1" min="1" max="8" width="10.71"/>
+    <col customWidth="1" min="9" max="9" width="43.57"/>
+    <col customWidth="1" min="10" max="31" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="43.5" customHeight="1">
@@ -4986,15 +5106,25 @@
         <v>99</v>
       </c>
       <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="8">
+        <v>3.0</v>
+      </c>
       <c r="L7" s="14"/>
-      <c r="M7" s="6"/>
+      <c r="M7" s="8">
+        <v>4.0</v>
+      </c>
       <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
+      <c r="O7" s="8">
+        <v>4.0</v>
+      </c>
       <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
+      <c r="Q7" s="8">
+        <v>3.0</v>
+      </c>
       <c r="R7" s="6"/>
-      <c r="S7" s="15"/>
+      <c r="S7" s="18">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="8" ht="126.75" customHeight="1">
       <c r="A8" s="10" t="s">
@@ -5025,15 +5155,25 @@
         <v>102</v>
       </c>
       <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="17"/>
+      <c r="K8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="N8" s="20"/>
+      <c r="O8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="R8" s="20"/>
+      <c r="S8" s="21">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="9" ht="126.75" customHeight="1">
       <c r="A9" s="10" t="s">
@@ -5064,15 +5204,25 @@
         <v>105</v>
       </c>
       <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="17"/>
+      <c r="K9" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="M9" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="N9" s="20"/>
+      <c r="O9" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="R9" s="20"/>
+      <c r="S9" s="21">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="10" ht="126.75" customHeight="1">
       <c r="A10" s="10" t="s">
@@ -5103,15 +5253,25 @@
         <v>108</v>
       </c>
       <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
+      <c r="K10" s="12">
+        <v>4.0</v>
+      </c>
       <c r="L10" s="16"/>
-      <c r="M10" s="10"/>
+      <c r="M10" s="12">
+        <v>4.0</v>
+      </c>
       <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
+      <c r="O10" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
+      <c r="Q10" s="12">
+        <v>4.0</v>
+      </c>
       <c r="R10" s="10"/>
-      <c r="S10" s="17"/>
+      <c r="S10" s="23">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="11" ht="126.75" customHeight="1">
       <c r="A11" s="10" t="s">
@@ -5142,15 +5302,25 @@
         <v>111</v>
       </c>
       <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
+      <c r="K11" s="12">
+        <v>4.0</v>
+      </c>
       <c r="L11" s="16"/>
-      <c r="M11" s="10"/>
+      <c r="M11" s="12">
+        <v>4.0</v>
+      </c>
       <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
+      <c r="O11" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
+      <c r="Q11" s="12">
+        <v>3.0</v>
+      </c>
       <c r="R11" s="10"/>
-      <c r="S11" s="17"/>
+      <c r="S11" s="23">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="12" ht="126.75" customHeight="1">
       <c r="A12" s="10" t="s">
@@ -5181,15 +5351,25 @@
         <v>114</v>
       </c>
       <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
+      <c r="K12" s="12">
+        <v>4.0</v>
+      </c>
       <c r="L12" s="16"/>
-      <c r="M12" s="10"/>
+      <c r="M12" s="12">
+        <v>4.0</v>
+      </c>
       <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
+      <c r="O12" s="12">
+        <v>5.0</v>
+      </c>
       <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
+      <c r="Q12" s="12">
+        <v>4.0</v>
+      </c>
       <c r="R12" s="10"/>
-      <c r="S12" s="17"/>
+      <c r="S12" s="23">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="13" ht="126.75" customHeight="1">
       <c r="A13" s="6" t="s">
@@ -5220,15 +5400,25 @@
         <v>117</v>
       </c>
       <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="15"/>
+      <c r="K13" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="L13" s="20"/>
+      <c r="M13" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="N13" s="20"/>
+      <c r="O13" s="19">
+        <v>3.0</v>
+      </c>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="19">
+        <v>4.0</v>
+      </c>
+      <c r="R13" s="20"/>
+      <c r="S13" s="21">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="14" ht="126.75" customHeight="1">
       <c r="A14" s="10" t="s">
@@ -5259,15 +5449,25 @@
         <v>120</v>
       </c>
       <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
+      <c r="K14" s="12">
+        <v>4.0</v>
+      </c>
       <c r="L14" s="16"/>
-      <c r="M14" s="10"/>
+      <c r="M14" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
+      <c r="O14" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="12">
+        <v>3.0</v>
+      </c>
       <c r="R14" s="10"/>
-      <c r="S14" s="17"/>
+      <c r="S14" s="23">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="15" ht="126.75" customHeight="1">
       <c r="A15" s="10" t="s">
@@ -5298,15 +5498,25 @@
         <v>123</v>
       </c>
       <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="K15" s="12">
+        <v>4.0</v>
+      </c>
       <c r="L15" s="16"/>
-      <c r="M15" s="10"/>
+      <c r="M15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
+      <c r="O15" s="12">
+        <v>3.0</v>
+      </c>
       <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
+      <c r="Q15" s="12">
+        <v>4.0</v>
+      </c>
       <c r="R15" s="10"/>
-      <c r="S15" s="17"/>
+      <c r="S15" s="23">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="16" ht="126.75" customHeight="1">
       <c r="A16" s="6" t="s">
@@ -5410,7 +5620,7 @@
       <c r="C18" s="11">
         <v>17.0</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="12" t="s">
         <v>130</v>
       </c>
       <c r="E18" s="10"/>
@@ -5425,15 +5635,25 @@
         <v>132</v>
       </c>
       <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
+      <c r="K18" s="12">
+        <v>3.0</v>
+      </c>
       <c r="L18" s="16"/>
-      <c r="M18" s="10"/>
+      <c r="M18" s="12">
+        <v>4.0</v>
+      </c>
       <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
+      <c r="O18" s="12">
+        <v>4.0</v>
+      </c>
       <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
+      <c r="Q18" s="12">
+        <v>3.0</v>
+      </c>
       <c r="R18" s="10"/>
-      <c r="S18" s="17"/>
+      <c r="S18" s="23">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="19" ht="126.75" customHeight="1">
       <c r="A19" s="6" t="s">
@@ -5443,7 +5663,7 @@
       <c r="C19" s="7">
         <v>18.0</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="8" t="s">
         <v>133</v>
       </c>
       <c r="E19" s="6"/>
@@ -5458,15 +5678,25 @@
         <v>135</v>
       </c>
       <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="K19" s="8">
+        <v>4.0</v>
+      </c>
       <c r="L19" s="14"/>
-      <c r="M19" s="6"/>
+      <c r="M19" s="8">
+        <v>4.0</v>
+      </c>
       <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
+      <c r="O19" s="8">
+        <v>4.0</v>
+      </c>
       <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
+      <c r="Q19" s="8">
+        <v>3.0</v>
+      </c>
       <c r="R19" s="6"/>
-      <c r="S19" s="15"/>
+      <c r="S19" s="18">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="20" ht="126.75" customHeight="1">
       <c r="A20" s="6" t="s">
@@ -6656,15 +6886,25 @@
         <v>146</v>
       </c>
       <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
+      <c r="K3" s="18">
+        <v>4.0</v>
+      </c>
       <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
+      <c r="M3" s="18">
+        <v>4.0</v>
+      </c>
       <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
+      <c r="O3" s="18">
+        <v>4.0</v>
+      </c>
       <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
+      <c r="Q3" s="18">
+        <v>4.0</v>
+      </c>
       <c r="R3" s="15"/>
-      <c r="S3" s="15"/>
+      <c r="S3" s="18">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="10" t="s">
@@ -7821,7 +8061,7 @@
       <c r="K2" s="18">
         <v>2.0</v>
       </c>
-      <c r="L2" s="19"/>
+      <c r="L2" s="24"/>
       <c r="M2" s="18">
         <v>2.0</v>
       </c>
@@ -7861,15 +8101,25 @@
         <v>156</v>
       </c>
       <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="17"/>
+      <c r="K3" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="L3" s="25"/>
+      <c r="M3" s="23">
+        <v>4.0</v>
+      </c>
       <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
+      <c r="O3" s="23">
+        <v>4.0</v>
+      </c>
       <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
+      <c r="Q3" s="23">
+        <v>5.0</v>
+      </c>
       <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
+      <c r="S3" s="23">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="15" t="s">
@@ -7892,12 +8142,12 @@
       <c r="H4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="26" t="s">
         <v>157</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
-      <c r="L4" s="19"/>
+      <c r="L4" s="24"/>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
@@ -7933,15 +8183,25 @@
         <v>160</v>
       </c>
       <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="17"/>
+      <c r="K5" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="L5" s="25"/>
+      <c r="M5" s="23">
+        <v>3.0</v>
+      </c>
       <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
+      <c r="O5" s="23">
+        <v>2.0</v>
+      </c>
       <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
+      <c r="Q5" s="23">
+        <v>3.0</v>
+      </c>
       <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
+      <c r="S5" s="23">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="6" ht="126.75" customHeight="1">
       <c r="A6" s="17" t="s">
@@ -7964,12 +8224,12 @@
       <c r="H6" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="27" t="s">
         <v>161</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
-      <c r="L6" s="20"/>
+      <c r="L6" s="25"/>
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
@@ -8005,15 +8265,25 @@
         <v>164</v>
       </c>
       <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="17"/>
+      <c r="K7" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="L7" s="25"/>
+      <c r="M7" s="23">
+        <v>4.0</v>
+      </c>
       <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
+      <c r="O7" s="23">
+        <v>5.0</v>
+      </c>
       <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
+      <c r="Q7" s="23">
+        <v>4.0</v>
+      </c>
       <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
+      <c r="S7" s="23">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="8" ht="126.75" customHeight="1">
       <c r="A8" s="15" t="s">
@@ -8036,12 +8306,12 @@
       <c r="H8" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="26" t="s">
         <v>165</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="19"/>
+      <c r="L8" s="24"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
@@ -8077,15 +8347,25 @@
         <v>168</v>
       </c>
       <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="15"/>
+      <c r="K9" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="L9" s="24"/>
+      <c r="M9" s="18">
+        <v>3.0</v>
+      </c>
       <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
+      <c r="O9" s="18">
+        <v>4.0</v>
+      </c>
       <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
+      <c r="Q9" s="18">
+        <v>4.0</v>
+      </c>
       <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
+      <c r="S9" s="18">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="10" ht="126.75" customHeight="1">
       <c r="A10" s="17" t="s">
@@ -8108,12 +8388,12 @@
       <c r="H10" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="27" t="s">
         <v>170</v>
       </c>
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
-      <c r="L10" s="20"/>
+      <c r="L10" s="25"/>
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -8154,7 +8434,7 @@
       <c r="K11" s="18">
         <v>2.0</v>
       </c>
-      <c r="L11" s="19"/>
+      <c r="L11" s="24"/>
       <c r="M11" s="18">
         <v>3.0</v>
       </c>
